--- a/basic_page.xlsx
+++ b/basic_page.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="17">
   <si>
     <t>CPT</t>
   </si>
@@ -44,25 +44,16 @@
     <t>menu not found on wordpress</t>
   </si>
   <si>
-    <t>/aac/</t>
-  </si>
-  <si>
-    <t>Menu matched</t>
-  </si>
-  <si>
-    <t>/accounting/</t>
-  </si>
-  <si>
-    <t>Menu not found on drupal and wp content is similar</t>
-  </si>
-  <si>
     <t>/rotc/</t>
   </si>
   <si>
     <t>Menu items missing on wordpress</t>
   </si>
   <si>
-    <t>/academic-program-finder/biochemistry/</t>
+    <t>biochemistry</t>
+  </si>
+  <si>
+    <t>/biochemistry</t>
   </si>
   <si>
     <t>"HOME" menu item missing from menu</t>
@@ -87,6 +78,9 @@
   </si>
   <si>
     <t>/geology/prospective_students/</t>
+  </si>
+  <si>
+    <t>/education/admissions</t>
   </si>
 </sst>
 </file>
@@ -1066,7 +1060,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
@@ -1093,7 +1087,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="34" spans="1:3">
+    <row r="3" ht="20.8" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1104,81 +1098,67 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" ht="101" spans="1:3">
+    <row r="4" ht="20.8" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="C4" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="5" ht="101" spans="1:3">
+    <row r="5" ht="34" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="6" ht="20.8" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="3" t="s">
+    <row r="6" ht="21" customHeight="1" spans="1:3">
+      <c r="A6" t="s">
         <v>11</v>
       </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="7" ht="34" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="2" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
         <v>13</v>
       </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="8" ht="21" customHeight="1" spans="1:3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" t="s">
-        <v>15</v>
-      </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/basic_page.xlsx
+++ b/basic_page.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="22">
   <si>
     <t>CPT</t>
   </si>
@@ -81,6 +81,21 @@
   </si>
   <si>
     <t>/education/admissions</t>
+  </si>
+  <si>
+    <t>/geology/faculty-staff</t>
+  </si>
+  <si>
+    <t>students/honor-societies</t>
+  </si>
+  <si>
+    <t>/students/honor-societies</t>
+  </si>
+  <si>
+    <t>news</t>
+  </si>
+  <si>
+    <t>/news</t>
   </si>
 </sst>
 </file>
@@ -1060,7 +1075,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
@@ -1161,6 +1176,30 @@
         <v>16</v>
       </c>
     </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/basic_page.xlsx
+++ b/basic_page.xlsx
@@ -89,7 +89,7 @@
     <t>students/honor-societies</t>
   </si>
   <si>
-    <t>/students/honor-societies</t>
+    <t>/linguistics/faculty-staff</t>
   </si>
   <si>
     <t>news</t>
@@ -108,7 +108,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -128,6 +128,13 @@
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF467886"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
     </font>
     <font>
       <u/>
@@ -592,141 +599,144 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1091,7 +1101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" ht="20.8" spans="1:3">
+    <row r="2" ht="22" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1102,7 +1112,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="20.8" spans="1:3">
+    <row r="3" ht="22" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1113,7 +1123,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" ht="20.8" spans="1:3">
+    <row r="4" ht="22" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1184,11 +1194,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" ht="18" spans="1:2">
       <c r="A11" t="s">
         <v>18</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1201,6 +1211,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B11" r:id="rId1" display="/linguistics/faculty-staff" tooltip="https://dev-suny-geneseo.pantheonsite.io/linguistics/faculty-staff"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
